--- a/experiments/01_term_expansion_by_model/report/dev_v1_original_no-few-shots_model_comparison.xlsx
+++ b/experiments/01_term_expansion_by_model/report/dev_v1_original_no-few-shots_model_comparison.xlsx
@@ -568,28 +568,28 @@
   <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
